--- a/output/20260430_181930/match_analysis.xlsx
+++ b/output/20260430_181930/match_analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/skc/Desktop/Work/PDS_current_4.28/pydantic_code/output/20260430_181930/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_7C4E2FC31078F29EE82B7094435DCE3A7744C4FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88BA3723-9F10-3A4F-BC24-7708B422B102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
